--- a/tools/productos_lista_importacion.xlsx
+++ b/tools/productos_lista_importacion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repos\Cleeny\tools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58F31EB8-A108-44FF-AD11-C2F70B99C75F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A881CC4-7B1B-4F4E-849D-F02C85EA0F4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1598,9 +1598,9 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="2" max="2" width="55.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.7109375" customWidth="1"/>
-    <col min="4" max="4" width="25" customWidth="1"/>
+    <col min="4" max="4" width="103" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.5703125" style="2" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
     <col min="7" max="7" width="28.140625" customWidth="1"/>

--- a/tools/productos_lista_importacion.xlsx
+++ b/tools/productos_lista_importacion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repos\Cleeny\tools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A881CC4-7B1B-4F4E-849D-F02C85EA0F4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1952BABF-DFE6-4F7C-9D98-1C3FB371BC6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1598,9 +1598,9 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="55.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
     <col min="3" max="3" width="17.7109375" customWidth="1"/>
-    <col min="4" max="4" width="103" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25" customWidth="1"/>
     <col min="5" max="5" width="16.5703125" style="2" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
     <col min="7" max="7" width="28.140625" customWidth="1"/>
@@ -1771,7 +1771,7 @@
         <v>6</v>
       </c>
       <c r="R3">
-        <v>1.1100000000000001</v>
+        <v>1.111111</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1822,7 +1822,7 @@
         <v>6</v>
       </c>
       <c r="R4">
-        <v>2.2200000000000002</v>
+        <v>2.2222219999999999</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1875,7 +1875,7 @@
         <v>6</v>
       </c>
       <c r="R5">
-        <v>5.77</v>
+        <v>5.7692310000000004</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1926,7 +1926,7 @@
         <v>6</v>
       </c>
       <c r="R6">
-        <v>1.1399999999999999</v>
+        <v>1.1363639999999999</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1979,7 +1979,7 @@
         <v>6</v>
       </c>
       <c r="R7">
-        <v>10.64</v>
+        <v>10.638298000000001</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -2030,7 +2030,7 @@
         <v>6</v>
       </c>
       <c r="R8">
-        <v>1.1100000000000001</v>
+        <v>1.111111</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -2081,7 +2081,7 @@
         <v>6</v>
       </c>
       <c r="R9">
-        <v>1.43</v>
+        <v>1.428571</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -2134,7 +2134,7 @@
         <v>6</v>
       </c>
       <c r="R10">
-        <v>7.41</v>
+        <v>7.4074070000000001</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -2185,7 +2185,7 @@
         <v>6</v>
       </c>
       <c r="R11">
-        <v>2.42</v>
+        <v>2.4193549999999999</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -2238,7 +2238,7 @@
         <v>6</v>
       </c>
       <c r="R12">
-        <v>7.41</v>
+        <v>7.4074070000000001</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2289,7 +2289,7 @@
         <v>6</v>
       </c>
       <c r="R13">
-        <v>2.42</v>
+        <v>2.4193549999999999</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2342,7 +2342,7 @@
         <v>6</v>
       </c>
       <c r="R14">
-        <v>13.33</v>
+        <v>13.333333</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2393,7 +2393,7 @@
         <v>6</v>
       </c>
       <c r="R15">
-        <v>2.2400000000000002</v>
+        <v>2.2388059999999999</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2548,7 +2548,7 @@
         <v>6</v>
       </c>
       <c r="R18">
-        <v>3.57</v>
+        <v>3.5714290000000002</v>
       </c>
     </row>
     <row r="19" spans="2:18">
@@ -2599,7 +2599,7 @@
         <v>6</v>
       </c>
       <c r="R19">
-        <v>7.69</v>
+        <v>7.6923079999999997</v>
       </c>
     </row>
     <row r="20" spans="2:18">
@@ -2650,7 +2650,7 @@
         <v>6</v>
       </c>
       <c r="R20">
-        <v>8.57</v>
+        <v>8.5714290000000002</v>
       </c>
     </row>
     <row r="21" spans="2:18">
@@ -2701,7 +2701,7 @@
         <v>6</v>
       </c>
       <c r="R21">
-        <v>2.2200000000000002</v>
+        <v>2.2222219999999999</v>
       </c>
     </row>
     <row r="22" spans="2:18">
@@ -2752,7 +2752,7 @@
         <v>6</v>
       </c>
       <c r="R22">
-        <v>3.92</v>
+        <v>3.9215689999999999</v>
       </c>
     </row>
     <row r="23" spans="2:18">
@@ -2803,7 +2803,7 @@
         <v>6</v>
       </c>
       <c r="R23">
-        <v>3.92</v>
+        <v>3.9215689999999999</v>
       </c>
     </row>
     <row r="24" spans="2:18">
@@ -2854,7 +2854,7 @@
         <v>6</v>
       </c>
       <c r="R24">
-        <v>3.45</v>
+        <v>3.4482759999999999</v>
       </c>
     </row>
     <row r="25" spans="2:18">
@@ -2905,7 +2905,7 @@
         <v>6</v>
       </c>
       <c r="R25">
-        <v>11.67</v>
+        <v>11.666667</v>
       </c>
     </row>
     <row r="26" spans="2:18">
@@ -2956,7 +2956,7 @@
         <v>6</v>
       </c>
       <c r="R26">
-        <v>7.69</v>
+        <v>7.6923079999999997</v>
       </c>
     </row>
     <row r="27" spans="2:18">
@@ -3007,7 +3007,7 @@
         <v>6</v>
       </c>
       <c r="R27">
-        <v>11.11</v>
+        <v>11.111110999999999</v>
       </c>
     </row>
     <row r="28" spans="2:18">
@@ -3109,7 +3109,7 @@
         <v>6</v>
       </c>
       <c r="R29">
-        <v>2.86</v>
+        <v>2.8571430000000002</v>
       </c>
     </row>
     <row r="30" spans="2:18">
@@ -3160,7 +3160,7 @@
         <v>6</v>
       </c>
       <c r="R30">
-        <v>5.71</v>
+        <v>5.7142860000000004</v>
       </c>
     </row>
     <row r="31" spans="2:18">
@@ -3262,7 +3262,7 @@
         <v>6</v>
       </c>
       <c r="R32">
-        <v>3.08</v>
+        <v>3.0769229999999999</v>
       </c>
     </row>
     <row r="33" spans="2:18">
@@ -3313,7 +3313,7 @@
         <v>6</v>
       </c>
       <c r="R33">
-        <v>5.88</v>
+        <v>5.8823530000000002</v>
       </c>
     </row>
     <row r="34" spans="2:18">
@@ -3415,7 +3415,7 @@
         <v>6</v>
       </c>
       <c r="R35">
-        <v>4.17</v>
+        <v>4.1666670000000003</v>
       </c>
     </row>
     <row r="36" spans="2:18">
@@ -3466,7 +3466,7 @@
         <v>6</v>
       </c>
       <c r="R36">
-        <v>3.33</v>
+        <v>3.3333330000000001</v>
       </c>
     </row>
     <row r="37" spans="2:18">
@@ -3517,7 +3517,7 @@
         <v>6</v>
       </c>
       <c r="R37">
-        <v>2.86</v>
+        <v>2.8571430000000002</v>
       </c>
     </row>
     <row r="38" spans="2:18">
@@ -3568,7 +3568,7 @@
         <v>6</v>
       </c>
       <c r="R38">
-        <v>2.67</v>
+        <v>2.6666669999999999</v>
       </c>
     </row>
     <row r="39" spans="2:18">
@@ -3619,7 +3619,7 @@
         <v>6</v>
       </c>
       <c r="R39">
-        <v>5.56</v>
+        <v>5.5555560000000002</v>
       </c>
     </row>
     <row r="40" spans="2:18">
@@ -3670,7 +3670,7 @@
         <v>6</v>
       </c>
       <c r="R40">
-        <v>4.6500000000000004</v>
+        <v>4.6511630000000004</v>
       </c>
     </row>
     <row r="41" spans="2:18">
@@ -3772,7 +3772,7 @@
         <v>6</v>
       </c>
       <c r="R42">
-        <v>14.29</v>
+        <v>14.285714</v>
       </c>
     </row>
     <row r="43" spans="2:18">
@@ -3823,7 +3823,7 @@
         <v>6</v>
       </c>
       <c r="R43">
-        <v>4.55</v>
+        <v>4.5454549999999996</v>
       </c>
     </row>
     <row r="44" spans="2:18">
@@ -3874,7 +3874,7 @@
         <v>6</v>
       </c>
       <c r="R44">
-        <v>7.14</v>
+        <v>7.1428570000000002</v>
       </c>
     </row>
     <row r="45" spans="2:18">
@@ -3925,7 +3925,7 @@
         <v>6</v>
       </c>
       <c r="R45">
-        <v>4.84</v>
+        <v>4.8387099999999998</v>
       </c>
     </row>
     <row r="46" spans="2:18">
@@ -4027,7 +4027,7 @@
         <v>6</v>
       </c>
       <c r="R47">
-        <v>14.29</v>
+        <v>14.285714</v>
       </c>
     </row>
     <row r="48" spans="2:18">
@@ -4129,7 +4129,7 @@
         <v>6</v>
       </c>
       <c r="R49">
-        <v>8.33</v>
+        <v>8.3333329999999997</v>
       </c>
     </row>
     <row r="50" spans="2:18">
@@ -4180,7 +4180,7 @@
         <v>6</v>
       </c>
       <c r="R50">
-        <v>7.14</v>
+        <v>7.1428570000000002</v>
       </c>
     </row>
     <row r="51" spans="2:18">
@@ -4231,7 +4231,7 @@
         <v>6</v>
       </c>
       <c r="R51">
-        <v>10.53</v>
+        <v>10.526316</v>
       </c>
     </row>
     <row r="52" spans="2:18">
@@ -4282,7 +4282,7 @@
         <v>6</v>
       </c>
       <c r="R52">
-        <v>10.53</v>
+        <v>10.526316</v>
       </c>
     </row>
     <row r="53" spans="2:18">
@@ -4333,7 +4333,7 @@
         <v>6</v>
       </c>
       <c r="R53">
-        <v>10.53</v>
+        <v>10.526316</v>
       </c>
     </row>
     <row r="54" spans="2:18">
@@ -4384,7 +4384,7 @@
         <v>6</v>
       </c>
       <c r="R54">
-        <v>3.85</v>
+        <v>3.8461539999999999</v>
       </c>
     </row>
     <row r="55" spans="2:18">
@@ -4435,7 +4435,7 @@
         <v>6</v>
       </c>
       <c r="R55">
-        <v>3.33</v>
+        <v>3.3333330000000001</v>
       </c>
     </row>
     <row r="56" spans="2:18">
@@ -4486,7 +4486,7 @@
         <v>6</v>
       </c>
       <c r="R56">
-        <v>6.67</v>
+        <v>6.6666670000000003</v>
       </c>
     </row>
     <row r="57" spans="2:18">
@@ -4537,7 +4537,7 @@
         <v>6</v>
       </c>
       <c r="R57">
-        <v>3.33</v>
+        <v>3.3333330000000001</v>
       </c>
     </row>
     <row r="58" spans="2:18">
@@ -4741,7 +4741,7 @@
         <v>6</v>
       </c>
       <c r="R61">
-        <v>11.11</v>
+        <v>11.111110999999999</v>
       </c>
     </row>
     <row r="62" spans="2:18">
@@ -4792,7 +4792,7 @@
         <v>6</v>
       </c>
       <c r="R62">
-        <v>8.33</v>
+        <v>8.3333329999999997</v>
       </c>
     </row>
     <row r="63" spans="2:18">
@@ -4843,7 +4843,7 @@
         <v>6</v>
       </c>
       <c r="R63">
-        <v>3.53</v>
+        <v>3.5294120000000002</v>
       </c>
     </row>
     <row r="64" spans="2:18">
@@ -4894,7 +4894,7 @@
         <v>6</v>
       </c>
       <c r="R64">
-        <v>16.670000000000002</v>
+        <v>16.666667</v>
       </c>
     </row>
     <row r="65" spans="2:18">
@@ -4996,7 +4996,7 @@
         <v>6</v>
       </c>
       <c r="R66">
-        <v>3.57</v>
+        <v>3.5714290000000002</v>
       </c>
     </row>
     <row r="67" spans="2:18">
@@ -5047,7 +5047,7 @@
         <v>6</v>
       </c>
       <c r="R67">
-        <v>4.55</v>
+        <v>4.5454549999999996</v>
       </c>
     </row>
     <row r="68" spans="2:18">
@@ -5098,7 +5098,7 @@
         <v>6</v>
       </c>
       <c r="R68">
-        <v>5.45</v>
+        <v>5.4545450000000004</v>
       </c>
     </row>
     <row r="69" spans="2:18">
@@ -5197,7 +5197,7 @@
         <v>6</v>
       </c>
       <c r="R70">
-        <v>5.88</v>
+        <v>5.8823530000000002</v>
       </c>
     </row>
     <row r="71" spans="2:18">
@@ -5248,7 +5248,7 @@
         <v>6</v>
       </c>
       <c r="R71">
-        <v>8.6999999999999993</v>
+        <v>8.6956520000000008</v>
       </c>
     </row>
     <row r="72" spans="2:18">
@@ -5350,7 +5350,7 @@
         <v>6</v>
       </c>
       <c r="R73">
-        <v>3.33</v>
+        <v>3.3333330000000001</v>
       </c>
     </row>
     <row r="74" spans="2:18">
@@ -5401,7 +5401,7 @@
         <v>6</v>
       </c>
       <c r="R74">
-        <v>5.45</v>
+        <v>5.4545450000000004</v>
       </c>
     </row>
     <row r="75" spans="2:18">
@@ -5452,7 +5452,7 @@
         <v>6</v>
       </c>
       <c r="R75">
-        <v>2.94</v>
+        <v>2.941176</v>
       </c>
     </row>
     <row r="76" spans="2:18">
@@ -5503,7 +5503,7 @@
         <v>6</v>
       </c>
       <c r="R76">
-        <v>2.27</v>
+        <v>2.2727270000000002</v>
       </c>
     </row>
     <row r="77" spans="2:18">
@@ -5554,7 +5554,7 @@
         <v>6</v>
       </c>
       <c r="R77">
-        <v>6.67</v>
+        <v>6.6666670000000003</v>
       </c>
     </row>
     <row r="78" spans="2:18">
@@ -5605,7 +5605,7 @@
         <v>6</v>
       </c>
       <c r="R78">
-        <v>5.45</v>
+        <v>5.4545450000000004</v>
       </c>
     </row>
     <row r="79" spans="2:18">
@@ -5707,7 +5707,7 @@
         <v>6</v>
       </c>
       <c r="R80">
-        <v>5.56</v>
+        <v>5.5555560000000002</v>
       </c>
     </row>
     <row r="81" spans="2:18">
@@ -5758,7 +5758,7 @@
         <v>6</v>
       </c>
       <c r="R81">
-        <v>7.69</v>
+        <v>7.6923079999999997</v>
       </c>
     </row>
     <row r="82" spans="2:18">
@@ -5860,7 +5860,7 @@
         <v>6</v>
       </c>
       <c r="R83">
-        <v>4.3499999999999996</v>
+        <v>4.3478260000000004</v>
       </c>
     </row>
     <row r="84" spans="2:18">
@@ -5911,7 +5911,7 @@
         <v>6</v>
       </c>
       <c r="R84">
-        <v>1.33</v>
+        <v>1.3333330000000001</v>
       </c>
     </row>
     <row r="85" spans="2:18">
@@ -5962,7 +5962,7 @@
         <v>6</v>
       </c>
       <c r="R85">
-        <v>11.11</v>
+        <v>11.111110999999999</v>
       </c>
     </row>
     <row r="86" spans="2:18">
@@ -6013,7 +6013,7 @@
         <v>6</v>
       </c>
       <c r="R86">
-        <v>3.53</v>
+        <v>3.5294120000000002</v>
       </c>
     </row>
     <row r="87" spans="2:18">
@@ -6064,7 +6064,7 @@
         <v>6</v>
       </c>
       <c r="R87">
-        <v>5.26</v>
+        <v>5.2631579999999998</v>
       </c>
     </row>
     <row r="88" spans="2:18">
@@ -6115,7 +6115,7 @@
         <v>6</v>
       </c>
       <c r="R88">
-        <v>5.45</v>
+        <v>5.4545450000000004</v>
       </c>
     </row>
     <row r="89" spans="2:18">
@@ -6166,7 +6166,7 @@
         <v>6</v>
       </c>
       <c r="R89">
-        <v>3.53</v>
+        <v>3.5294120000000002</v>
       </c>
     </row>
     <row r="90" spans="2:18">
@@ -6217,7 +6217,7 @@
         <v>6</v>
       </c>
       <c r="R90">
-        <v>4.62</v>
+        <v>4.6153849999999998</v>
       </c>
     </row>
     <row r="91" spans="2:18">
@@ -6268,7 +6268,7 @@
         <v>6</v>
       </c>
       <c r="R91">
-        <v>5.71</v>
+        <v>5.7142860000000004</v>
       </c>
     </row>
     <row r="92" spans="2:18">
@@ -6319,7 +6319,7 @@
         <v>6</v>
       </c>
       <c r="R92">
-        <v>13.33</v>
+        <v>13.333333</v>
       </c>
     </row>
     <row r="93" spans="2:18">
@@ -6421,7 +6421,7 @@
         <v>6</v>
       </c>
       <c r="R94">
-        <v>6.67</v>
+        <v>6.6666670000000003</v>
       </c>
     </row>
     <row r="95" spans="2:18">
@@ -6472,7 +6472,7 @@
         <v>6</v>
       </c>
       <c r="R95">
-        <v>6.67</v>
+        <v>6.6666670000000003</v>
       </c>
     </row>
     <row r="96" spans="2:18">
@@ -6523,7 +6523,7 @@
         <v>6</v>
       </c>
       <c r="R96">
-        <v>3.64</v>
+        <v>3.6363639999999999</v>
       </c>
     </row>
     <row r="97" spans="2:18">
@@ -6574,7 +6574,7 @@
         <v>6</v>
       </c>
       <c r="R97">
-        <v>3.53</v>
+        <v>3.5294120000000002</v>
       </c>
     </row>
     <row r="98" spans="2:18">
@@ -6676,7 +6676,7 @@
         <v>6</v>
       </c>
       <c r="R99">
-        <v>11.11</v>
+        <v>11.111110999999999</v>
       </c>
     </row>
     <row r="100" spans="2:18">
@@ -6727,7 +6727,7 @@
         <v>6</v>
       </c>
       <c r="R100">
-        <v>4.55</v>
+        <v>4.5454549999999996</v>
       </c>
     </row>
     <row r="101" spans="2:18">
@@ -6778,7 +6778,7 @@
         <v>6</v>
       </c>
       <c r="R101">
-        <v>5.45</v>
+        <v>5.4545450000000004</v>
       </c>
     </row>
     <row r="102" spans="2:18">
@@ -6931,7 +6931,7 @@
         <v>6</v>
       </c>
       <c r="R104">
-        <v>1.33</v>
+        <v>1.3333330000000001</v>
       </c>
     </row>
     <row r="105" spans="2:18">
@@ -6982,7 +6982,7 @@
         <v>6</v>
       </c>
       <c r="R105">
-        <v>6.67</v>
+        <v>6.6666670000000003</v>
       </c>
     </row>
     <row r="106" spans="2:18">
@@ -7084,7 +7084,7 @@
         <v>6</v>
       </c>
       <c r="R107">
-        <v>4.55</v>
+        <v>4.5454549999999996</v>
       </c>
     </row>
     <row r="108" spans="2:18">
@@ -7135,7 +7135,7 @@
         <v>6</v>
       </c>
       <c r="R108">
-        <v>4.55</v>
+        <v>4.5454549999999996</v>
       </c>
     </row>
     <row r="109" spans="2:18">
@@ -7186,7 +7186,7 @@
         <v>6</v>
       </c>
       <c r="R109">
-        <v>4.08</v>
+        <v>4.0816330000000001</v>
       </c>
     </row>
     <row r="110" spans="2:18">
@@ -7237,7 +7237,7 @@
         <v>6</v>
       </c>
       <c r="R110">
-        <v>4.4400000000000004</v>
+        <v>4.4444439999999998</v>
       </c>
     </row>
     <row r="111" spans="2:18">
@@ -7288,7 +7288,7 @@
         <v>6</v>
       </c>
       <c r="R111">
-        <v>9.52</v>
+        <v>9.5238099999999992</v>
       </c>
     </row>
     <row r="112" spans="2:18">
@@ -7390,7 +7390,7 @@
         <v>6</v>
       </c>
       <c r="R113">
-        <v>1.67</v>
+        <v>1.6666669999999999</v>
       </c>
     </row>
     <row r="114" spans="2:18">
@@ -7441,7 +7441,7 @@
         <v>6</v>
       </c>
       <c r="R114">
-        <v>4.17</v>
+        <v>4.1666670000000003</v>
       </c>
     </row>
     <row r="115" spans="2:18">
@@ -7543,7 +7543,7 @@
         <v>6</v>
       </c>
       <c r="R116">
-        <v>2.69</v>
+        <v>2.6881719999999998</v>
       </c>
     </row>
     <row r="117" spans="2:18">
@@ -7594,7 +7594,7 @@
         <v>6</v>
       </c>
       <c r="R117">
-        <v>14.29</v>
+        <v>14.285714</v>
       </c>
     </row>
     <row r="118" spans="2:18">
@@ -7645,7 +7645,7 @@
         <v>6</v>
       </c>
       <c r="R118">
-        <v>1.96</v>
+        <v>1.9607840000000001</v>
       </c>
     </row>
     <row r="119" spans="2:18">
@@ -7696,7 +7696,7 @@
         <v>6</v>
       </c>
       <c r="R119">
-        <v>4.17</v>
+        <v>4.1666670000000003</v>
       </c>
     </row>
     <row r="120" spans="2:18">
@@ -7747,7 +7747,7 @@
         <v>6</v>
       </c>
       <c r="R120">
-        <v>2.7</v>
+        <v>2.7027030000000001</v>
       </c>
     </row>
     <row r="121" spans="2:18">
@@ -7798,7 +7798,7 @@
         <v>6</v>
       </c>
       <c r="R121">
-        <v>6.67</v>
+        <v>6.6666670000000003</v>
       </c>
     </row>
     <row r="122" spans="2:18">
@@ -7849,7 +7849,7 @@
         <v>6</v>
       </c>
       <c r="R122">
-        <v>1.37</v>
+        <v>1.3698630000000001</v>
       </c>
     </row>
     <row r="123" spans="2:18">
@@ -7900,7 +7900,7 @@
         <v>6</v>
       </c>
       <c r="R123">
-        <v>16.670000000000002</v>
+        <v>16.666667</v>
       </c>
     </row>
     <row r="124" spans="2:18">
@@ -7951,7 +7951,7 @@
         <v>6</v>
       </c>
       <c r="R124">
-        <v>7.14</v>
+        <v>7.1428570000000002</v>
       </c>
     </row>
     <row r="125" spans="2:18">
@@ -8002,7 +8002,7 @@
         <v>6</v>
       </c>
       <c r="R125">
-        <v>5.88</v>
+        <v>5.8823530000000002</v>
       </c>
     </row>
     <row r="126" spans="2:18">
@@ -8155,7 +8155,7 @@
         <v>6</v>
       </c>
       <c r="R128">
-        <v>3.16</v>
+        <v>3.1578949999999999</v>
       </c>
     </row>
     <row r="129" spans="2:18">
@@ -8206,7 +8206,7 @@
         <v>6</v>
       </c>
       <c r="R129">
-        <v>7.14</v>
+        <v>7.1428570000000002</v>
       </c>
     </row>
     <row r="130" spans="2:18">
@@ -8257,7 +8257,7 @@
         <v>6</v>
       </c>
       <c r="R130">
-        <v>2.86</v>
+        <v>2.8571430000000002</v>
       </c>
     </row>
     <row r="131" spans="2:18">
@@ -8308,7 +8308,7 @@
         <v>6</v>
       </c>
       <c r="R131">
-        <v>3.85</v>
+        <v>3.8461539999999999</v>
       </c>
     </row>
     <row r="132" spans="2:18">
@@ -8410,7 +8410,7 @@
         <v>6</v>
       </c>
       <c r="R133">
-        <v>8.33</v>
+        <v>8.3333329999999997</v>
       </c>
     </row>
     <row r="134" spans="2:18">
@@ -8512,7 +8512,7 @@
         <v>6</v>
       </c>
       <c r="R135">
-        <v>3.33</v>
+        <v>3.3333330000000001</v>
       </c>
     </row>
     <row r="136" spans="2:18">
@@ -8614,7 +8614,7 @@
         <v>6</v>
       </c>
       <c r="R137">
-        <v>3.28</v>
+        <v>3.278689</v>
       </c>
     </row>
     <row r="138" spans="2:18">
@@ -8665,7 +8665,7 @@
         <v>6</v>
       </c>
       <c r="R138">
-        <v>6.67</v>
+        <v>6.6666670000000003</v>
       </c>
     </row>
     <row r="139" spans="2:18">
@@ -8716,7 +8716,7 @@
         <v>6</v>
       </c>
       <c r="R139">
-        <v>16.670000000000002</v>
+        <v>16.666667</v>
       </c>
     </row>
     <row r="140" spans="2:18">
@@ -8767,7 +8767,7 @@
         <v>6</v>
       </c>
       <c r="R140">
-        <v>16.670000000000002</v>
+        <v>16.666667</v>
       </c>
     </row>
     <row r="141" spans="2:18">
@@ -8818,7 +8818,7 @@
         <v>6</v>
       </c>
       <c r="R141">
-        <v>9.09</v>
+        <v>9.0909089999999999</v>
       </c>
     </row>
     <row r="142" spans="2:18">
@@ -8869,7 +8869,7 @@
         <v>6</v>
       </c>
       <c r="R142">
-        <v>5.88</v>
+        <v>5.8823530000000002</v>
       </c>
     </row>
     <row r="143" spans="2:18">
@@ -8971,7 +8971,7 @@
         <v>6</v>
       </c>
       <c r="R144">
-        <v>3.85</v>
+        <v>3.8461539999999999</v>
       </c>
     </row>
     <row r="145" spans="2:18">
@@ -9022,7 +9022,7 @@
         <v>6</v>
       </c>
       <c r="R145">
-        <v>4.17</v>
+        <v>4.1666670000000003</v>
       </c>
     </row>
     <row r="146" spans="2:18">
@@ -9124,7 +9124,7 @@
         <v>6</v>
       </c>
       <c r="R147">
-        <v>1.43</v>
+        <v>1.428571</v>
       </c>
     </row>
     <row r="148" spans="2:18">
@@ -9634,7 +9634,7 @@
         <v>20</v>
       </c>
       <c r="R157">
-        <v>6.67</v>
+        <v>6.6666670000000003</v>
       </c>
     </row>
     <row r="158" spans="2:18">
@@ -9685,7 +9685,7 @@
         <v>20</v>
       </c>
       <c r="R158">
-        <v>20.83</v>
+        <v>20.833333</v>
       </c>
     </row>
     <row r="159" spans="2:18">
@@ -9736,7 +9736,7 @@
         <v>20</v>
       </c>
       <c r="R159">
-        <v>20.83</v>
+        <v>20.833333</v>
       </c>
     </row>
     <row r="160" spans="2:18">
@@ -9787,7 +9787,7 @@
         <v>20</v>
       </c>
       <c r="R160">
-        <v>14.29</v>
+        <v>14.285714</v>
       </c>
     </row>
     <row r="161" spans="2:18">
@@ -9838,7 +9838,7 @@
         <v>20</v>
       </c>
       <c r="R161">
-        <v>5.41</v>
+        <v>5.405405</v>
       </c>
     </row>
     <row r="162" spans="2:18">
@@ -9889,7 +9889,7 @@
         <v>20</v>
       </c>
       <c r="R162">
-        <v>10.71</v>
+        <v>10.714286</v>
       </c>
     </row>
     <row r="163" spans="2:18">
@@ -9940,7 +9940,7 @@
         <v>20</v>
       </c>
       <c r="R163">
-        <v>10.53</v>
+        <v>10.526316</v>
       </c>
     </row>
     <row r="164" spans="2:18">
@@ -9991,7 +9991,7 @@
         <v>20</v>
       </c>
       <c r="R164">
-        <v>6.52</v>
+        <v>6.5217390000000002</v>
       </c>
     </row>
     <row r="165" spans="2:18">
@@ -10042,7 +10042,7 @@
         <v>20</v>
       </c>
       <c r="R165">
-        <v>13.51</v>
+        <v>13.513514000000001</v>
       </c>
     </row>
     <row r="166" spans="2:18">
@@ -10093,7 +10093,7 @@
         <v>20</v>
       </c>
       <c r="R166">
-        <v>13.51</v>
+        <v>13.513514000000001</v>
       </c>
     </row>
     <row r="167" spans="2:18">
@@ -10144,7 +10144,7 @@
         <v>20</v>
       </c>
       <c r="R167">
-        <v>11.63</v>
+        <v>11.627907</v>
       </c>
     </row>
     <row r="168" spans="2:18">
@@ -10195,7 +10195,7 @@
         <v>20</v>
       </c>
       <c r="R168">
-        <v>11.63</v>
+        <v>11.627907</v>
       </c>
     </row>
     <row r="169" spans="2:18">
@@ -10246,7 +10246,7 @@
         <v>20</v>
       </c>
       <c r="R169">
-        <v>3.33</v>
+        <v>3.3333330000000001</v>
       </c>
     </row>
     <row r="170" spans="2:18">
@@ -10297,7 +10297,7 @@
         <v>20</v>
       </c>
       <c r="R170">
-        <v>9.52</v>
+        <v>9.5238099999999992</v>
       </c>
     </row>
     <row r="171" spans="2:18">
@@ -10348,7 +10348,7 @@
         <v>20</v>
       </c>
       <c r="R171">
-        <v>9.52</v>
+        <v>9.5238099999999992</v>
       </c>
     </row>
     <row r="172" spans="2:18">
@@ -10501,7 +10501,7 @@
         <v>20</v>
       </c>
       <c r="R174">
-        <v>28.57</v>
+        <v>28.571428999999998</v>
       </c>
     </row>
     <row r="175" spans="2:18">
@@ -10705,7 +10705,7 @@
         <v>20</v>
       </c>
       <c r="R178">
-        <v>30.43</v>
+        <v>30.434782999999999</v>
       </c>
     </row>
     <row r="179" spans="2:18">
@@ -10756,7 +10756,7 @@
         <v>20</v>
       </c>
       <c r="R179">
-        <v>29.63</v>
+        <v>29.629629999999999</v>
       </c>
     </row>
     <row r="180" spans="2:18">
@@ -10858,7 +10858,7 @@
         <v>20</v>
       </c>
       <c r="R181">
-        <v>28.57</v>
+        <v>28.571428999999998</v>
       </c>
     </row>
     <row r="182" spans="2:18">
@@ -10909,7 +10909,7 @@
         <v>20</v>
       </c>
       <c r="R182">
-        <v>20.83</v>
+        <v>20.833333</v>
       </c>
     </row>
     <row r="183" spans="2:18">
@@ -10960,7 +10960,7 @@
         <v>20</v>
       </c>
       <c r="R183">
-        <v>20.83</v>
+        <v>20.833333</v>
       </c>
     </row>
     <row r="184" spans="2:18">
@@ -11011,7 +11011,7 @@
         <v>20</v>
       </c>
       <c r="R184">
-        <v>20.83</v>
+        <v>20.833333</v>
       </c>
     </row>
     <row r="185" spans="2:18">
@@ -11059,7 +11059,7 @@
         <v>20</v>
       </c>
       <c r="R185">
-        <v>5.45</v>
+        <v>5.4545450000000004</v>
       </c>
     </row>
     <row r="186" spans="2:18">
@@ -11107,7 +11107,7 @@
         <v>20</v>
       </c>
       <c r="R186">
-        <v>5.88</v>
+        <v>5.8823530000000002</v>
       </c>
     </row>
     <row r="187" spans="2:18">
@@ -11155,7 +11155,7 @@
         <v>20</v>
       </c>
       <c r="R187">
-        <v>7.89</v>
+        <v>7.8947370000000001</v>
       </c>
     </row>
     <row r="188" spans="2:18">
@@ -11203,7 +11203,7 @@
         <v>20</v>
       </c>
       <c r="R188">
-        <v>4.26</v>
+        <v>4.2553190000000001</v>
       </c>
     </row>
     <row r="189" spans="2:18">
@@ -11251,7 +11251,7 @@
         <v>20</v>
       </c>
       <c r="R189">
-        <v>8.77</v>
+        <v>8.7719299999999993</v>
       </c>
     </row>
     <row r="190" spans="2:18">
@@ -11299,7 +11299,7 @@
         <v>20</v>
       </c>
       <c r="R190">
-        <v>8.77</v>
+        <v>8.7719299999999993</v>
       </c>
     </row>
     <row r="191" spans="2:18">
@@ -11347,7 +11347,7 @@
         <v>20</v>
       </c>
       <c r="R191">
-        <v>7.94</v>
+        <v>7.9365079999999999</v>
       </c>
     </row>
     <row r="192" spans="2:18">
@@ -11395,7 +11395,7 @@
         <v>20</v>
       </c>
       <c r="R192">
-        <v>7.94</v>
+        <v>7.9365079999999999</v>
       </c>
     </row>
     <row r="193" spans="2:18">
@@ -11443,7 +11443,7 @@
         <v>20</v>
       </c>
       <c r="R193">
-        <v>14.67</v>
+        <v>14.666667</v>
       </c>
     </row>
     <row r="194" spans="2:18">
@@ -11539,7 +11539,7 @@
         <v>20</v>
       </c>
       <c r="R195">
-        <v>8.57</v>
+        <v>8.5714290000000002</v>
       </c>
     </row>
     <row r="196" spans="2:18">
@@ -11587,7 +11587,7 @@
         <v>20</v>
       </c>
       <c r="R196">
-        <v>8.57</v>
+        <v>8.5714290000000002</v>
       </c>
     </row>
     <row r="197" spans="2:18">
@@ -11635,7 +11635,7 @@
         <v>20</v>
       </c>
       <c r="R197">
-        <v>8.57</v>
+        <v>8.5714290000000002</v>
       </c>
     </row>
     <row r="198" spans="2:18">
@@ -11683,7 +11683,7 @@
         <v>20</v>
       </c>
       <c r="R198">
-        <v>16.28</v>
+        <v>16.279070000000001</v>
       </c>
     </row>
     <row r="199" spans="2:18">
@@ -11731,7 +11731,7 @@
         <v>20</v>
       </c>
       <c r="R199">
-        <v>17.02</v>
+        <v>17.021277000000001</v>
       </c>
     </row>
     <row r="200" spans="2:18">
@@ -11779,7 +11779,7 @@
         <v>20</v>
       </c>
       <c r="R200">
-        <v>11.36</v>
+        <v>11.363636</v>
       </c>
     </row>
     <row r="201" spans="2:18">
@@ -11827,7 +11827,7 @@
         <v>20</v>
       </c>
       <c r="R201">
-        <v>11.36</v>
+        <v>11.363636</v>
       </c>
     </row>
     <row r="202" spans="2:18">

--- a/tools/productos_lista_importacion.xlsx
+++ b/tools/productos_lista_importacion.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repos\Cleeny\tools\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manuel Alfaro\Documents\Desarrollos\Cleeny\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62E9DAEC-80DD-43E8-817E-83C91E879217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E058ADEC-3B4D-4D5F-B490-8506A6AF8A1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1287,7 +1287,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1304,6 +1304,12 @@
         <fgColor rgb="FF27AE60"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1317,12 +1323,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1629,7 +1636,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="2" max="2" width="55.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.5703125" customWidth="1"/>
     <col min="4" max="4" width="22.7109375" customWidth="1"/>
     <col min="5" max="5" width="15.85546875" style="2" customWidth="1"/>
@@ -9871,7 +9878,7 @@
         <v>107.75862100000001</v>
       </c>
     </row>
-    <row r="145" spans="2:20">
+    <row r="145" spans="1:20">
       <c r="B145" t="s">
         <v>238</v>
       </c>
@@ -9928,7 +9935,7 @@
         <v>99.137930999999995</v>
       </c>
     </row>
-    <row r="146" spans="2:20">
+    <row r="146" spans="1:20">
       <c r="B146" t="s">
         <v>240</v>
       </c>
@@ -9985,7 +9992,7 @@
         <v>81.896552</v>
       </c>
     </row>
-    <row r="147" spans="2:20">
+    <row r="147" spans="1:20">
       <c r="B147" t="s">
         <v>241</v>
       </c>
@@ -10042,7 +10049,7 @@
         <v>297.413793</v>
       </c>
     </row>
-    <row r="148" spans="2:20">
+    <row r="148" spans="1:20">
       <c r="B148" t="s">
         <v>242</v>
       </c>
@@ -10096,7 +10103,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="149" spans="2:20">
+    <row r="149" spans="1:20">
       <c r="B149" t="s">
         <v>243</v>
       </c>
@@ -10150,7 +10157,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="150" spans="2:20">
+    <row r="150" spans="1:20">
       <c r="B150" t="s">
         <v>244</v>
       </c>
@@ -10204,7 +10211,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="151" spans="2:20">
+    <row r="151" spans="1:20">
       <c r="B151" t="s">
         <v>245</v>
       </c>
@@ -10258,7 +10265,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="152" spans="2:20">
+    <row r="152" spans="1:20">
       <c r="B152" t="s">
         <v>246</v>
       </c>
@@ -10312,7 +10319,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="153" spans="2:20">
+    <row r="153" spans="1:20">
       <c r="B153" t="s">
         <v>248</v>
       </c>
@@ -10366,7 +10373,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="154" spans="2:20">
+    <row r="154" spans="1:20">
       <c r="B154" t="s">
         <v>249</v>
       </c>
@@ -10420,7 +10427,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="155" spans="2:20">
+    <row r="155" spans="1:20">
       <c r="B155" t="s">
         <v>250</v>
       </c>
@@ -10474,7 +10481,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="156" spans="2:20">
+    <row r="156" spans="1:20">
       <c r="B156" t="s">
         <v>251</v>
       </c>
@@ -10528,1657 +10535,1687 @@
         <v>6</v>
       </c>
     </row>
-    <row r="157" spans="2:20">
-      <c r="B157" t="s">
+    <row r="157" spans="1:20">
+      <c r="A157" s="5"/>
+      <c r="B157" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="C157" t="s">
+      <c r="C157" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="D157" t="s">
+      <c r="D157" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="E157"/>
-      <c r="F157">
-        <v>1</v>
-      </c>
-      <c r="G157" t="s">
+      <c r="E157" s="5"/>
+      <c r="F157" s="5">
+        <v>1</v>
+      </c>
+      <c r="G157" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="H157">
+      <c r="H157" s="5">
         <v>18.103448</v>
       </c>
-      <c r="I157">
+      <c r="I157" s="5">
         <v>38.793103000000002</v>
       </c>
-      <c r="J157" t="s">
-        <v>25</v>
-      </c>
-      <c r="K157" t="s">
-        <v>25</v>
-      </c>
-      <c r="L157" t="s">
+      <c r="J157" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K157" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L157" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="M157" t="s">
-        <v>27</v>
-      </c>
-      <c r="N157" t="s">
-        <v>27</v>
-      </c>
-      <c r="O157" t="s">
-        <v>28</v>
-      </c>
-      <c r="P157">
-        <v>0</v>
-      </c>
-      <c r="Q157">
-        <v>0</v>
-      </c>
-      <c r="R157" t="s">
-        <v>28</v>
-      </c>
-      <c r="S157">
+      <c r="M157" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N157" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O157" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P157" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q157" s="5">
+        <v>0</v>
+      </c>
+      <c r="R157" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="S157" s="5">
         <v>20</v>
       </c>
-      <c r="T157">
+      <c r="T157" s="5">
         <v>36.206896999999998</v>
       </c>
     </row>
-    <row r="158" spans="2:20">
-      <c r="B158" t="s">
+    <row r="158" spans="1:20">
+      <c r="A158" s="5"/>
+      <c r="B158" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="C158" t="s">
+      <c r="C158" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="D158" t="s">
+      <c r="D158" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="E158"/>
-      <c r="F158">
-        <v>1</v>
-      </c>
-      <c r="G158" t="s">
+      <c r="E158" s="5"/>
+      <c r="F158" s="5">
+        <v>1</v>
+      </c>
+      <c r="G158" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="H158">
+      <c r="H158" s="5">
         <v>6.0344829999999998</v>
       </c>
-      <c r="I158">
+      <c r="I158" s="5">
         <v>10.344828</v>
       </c>
-      <c r="J158" t="s">
-        <v>25</v>
-      </c>
-      <c r="K158" t="s">
-        <v>25</v>
-      </c>
-      <c r="L158" t="s">
+      <c r="J158" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K158" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L158" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="M158" t="s">
-        <v>27</v>
-      </c>
-      <c r="N158" t="s">
-        <v>27</v>
-      </c>
-      <c r="O158" t="s">
-        <v>28</v>
-      </c>
-      <c r="P158">
-        <v>0</v>
-      </c>
-      <c r="Q158">
-        <v>0</v>
-      </c>
-      <c r="R158" t="s">
-        <v>28</v>
-      </c>
-      <c r="S158">
+      <c r="M158" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N158" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O158" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P158" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q158" s="5">
+        <v>0</v>
+      </c>
+      <c r="R158" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="S158" s="5">
         <v>20</v>
       </c>
-      <c r="T158">
+      <c r="T158" s="5">
         <v>8.1896550000000001</v>
       </c>
     </row>
-    <row r="159" spans="2:20">
-      <c r="B159" t="s">
+    <row r="159" spans="1:20">
+      <c r="A159" s="5"/>
+      <c r="B159" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="C159" t="s">
+      <c r="C159" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="D159" t="s">
+      <c r="D159" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="E159"/>
-      <c r="F159">
-        <v>1</v>
-      </c>
-      <c r="G159" t="s">
+      <c r="E159" s="5"/>
+      <c r="F159" s="5">
+        <v>1</v>
+      </c>
+      <c r="G159" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="H159">
+      <c r="H159" s="5">
         <v>6.0344829999999998</v>
       </c>
-      <c r="I159">
+      <c r="I159" s="5">
         <v>10.344828</v>
       </c>
-      <c r="J159" t="s">
-        <v>25</v>
-      </c>
-      <c r="K159" t="s">
-        <v>25</v>
-      </c>
-      <c r="L159" t="s">
+      <c r="J159" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K159" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L159" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="M159" t="s">
-        <v>27</v>
-      </c>
-      <c r="N159" t="s">
-        <v>27</v>
-      </c>
-      <c r="O159" t="s">
-        <v>28</v>
-      </c>
-      <c r="P159">
-        <v>0</v>
-      </c>
-      <c r="Q159">
-        <v>0</v>
-      </c>
-      <c r="R159" t="s">
-        <v>28</v>
-      </c>
-      <c r="S159">
+      <c r="M159" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N159" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O159" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P159" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q159" s="5">
+        <v>0</v>
+      </c>
+      <c r="R159" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="S159" s="5">
         <v>20</v>
       </c>
-      <c r="T159">
+      <c r="T159" s="5">
         <v>8.1896550000000001</v>
       </c>
     </row>
-    <row r="160" spans="2:20">
-      <c r="B160" t="s">
+    <row r="160" spans="1:20">
+      <c r="A160" s="5"/>
+      <c r="B160" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="C160" t="s">
-        <v>40</v>
-      </c>
-      <c r="D160" t="s">
+      <c r="C160" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D160" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="E160"/>
-      <c r="F160">
-        <v>1</v>
-      </c>
-      <c r="G160" t="s">
+      <c r="E160" s="5"/>
+      <c r="F160" s="5">
+        <v>1</v>
+      </c>
+      <c r="G160" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="H160">
+      <c r="H160" s="5">
         <v>2.3706900000000002</v>
       </c>
-      <c r="I160">
+      <c r="I160" s="5">
         <v>6.0344829999999998</v>
       </c>
-      <c r="J160" t="s">
-        <v>25</v>
-      </c>
-      <c r="K160" t="s">
-        <v>25</v>
-      </c>
-      <c r="L160" t="s">
+      <c r="J160" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K160" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L160" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="M160" t="s">
-        <v>27</v>
-      </c>
-      <c r="N160" t="s">
-        <v>27</v>
-      </c>
-      <c r="O160" t="s">
-        <v>28</v>
-      </c>
-      <c r="P160">
-        <v>0</v>
-      </c>
-      <c r="Q160">
-        <v>0</v>
-      </c>
-      <c r="R160" t="s">
-        <v>28</v>
-      </c>
-      <c r="S160">
+      <c r="M160" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N160" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O160" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P160" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q160" s="5">
+        <v>0</v>
+      </c>
+      <c r="R160" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="S160" s="5">
         <v>20</v>
       </c>
-      <c r="T160">
+      <c r="T160" s="5">
         <v>5.1724139999999998</v>
       </c>
     </row>
-    <row r="161" spans="2:20">
-      <c r="B161" t="s">
+    <row r="161" spans="1:20">
+      <c r="A161" s="5"/>
+      <c r="B161" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="C161" t="s">
-        <v>40</v>
-      </c>
-      <c r="D161" t="s">
+      <c r="C161" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D161" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="E161"/>
-      <c r="F161">
-        <v>1</v>
-      </c>
-      <c r="G161" t="s">
+      <c r="E161" s="5"/>
+      <c r="F161" s="5">
+        <v>1</v>
+      </c>
+      <c r="G161" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="H161">
+      <c r="H161" s="5">
         <v>20.689654999999998</v>
       </c>
-      <c r="I161">
+      <c r="I161" s="5">
         <v>31.896552</v>
       </c>
-      <c r="J161" t="s">
-        <v>25</v>
-      </c>
-      <c r="K161" t="s">
-        <v>25</v>
-      </c>
-      <c r="L161" t="s">
+      <c r="J161" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K161" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L161" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="M161" t="s">
-        <v>27</v>
-      </c>
-      <c r="N161" t="s">
-        <v>27</v>
-      </c>
-      <c r="O161" t="s">
-        <v>28</v>
-      </c>
-      <c r="P161">
-        <v>0</v>
-      </c>
-      <c r="Q161">
-        <v>0</v>
-      </c>
-      <c r="R161" t="s">
-        <v>28</v>
-      </c>
-      <c r="S161">
+      <c r="M161" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N161" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O161" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P161" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q161" s="5">
+        <v>0</v>
+      </c>
+      <c r="R161" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="S161" s="5">
         <v>20</v>
       </c>
-      <c r="T161">
+      <c r="T161" s="5">
         <v>30.172414</v>
       </c>
     </row>
-    <row r="162" spans="2:20">
-      <c r="B162" t="s">
+    <row r="162" spans="1:20">
+      <c r="A162" s="5"/>
+      <c r="B162" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="C162" t="s">
-        <v>40</v>
-      </c>
-      <c r="D162" t="s">
+      <c r="C162" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D162" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="E162"/>
-      <c r="F162">
-        <v>1</v>
-      </c>
-      <c r="G162" t="s">
+      <c r="E162" s="5"/>
+      <c r="F162" s="5">
+        <v>1</v>
+      </c>
+      <c r="G162" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="H162">
+      <c r="H162" s="5">
         <v>14.655172</v>
       </c>
-      <c r="I162">
+      <c r="I162" s="5">
         <v>24.137930999999998</v>
       </c>
-      <c r="J162" t="s">
-        <v>25</v>
-      </c>
-      <c r="K162" t="s">
-        <v>25</v>
-      </c>
-      <c r="L162" t="s">
+      <c r="J162" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K162" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L162" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="M162" t="s">
-        <v>27</v>
-      </c>
-      <c r="N162" t="s">
-        <v>27</v>
-      </c>
-      <c r="O162" t="s">
-        <v>28</v>
-      </c>
-      <c r="P162">
-        <v>0</v>
-      </c>
-      <c r="Q162">
-        <v>0</v>
-      </c>
-      <c r="R162" t="s">
-        <v>28</v>
-      </c>
-      <c r="S162">
+      <c r="M162" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N162" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O162" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P162" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q162" s="5">
+        <v>0</v>
+      </c>
+      <c r="R162" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="S162" s="5">
         <v>20</v>
       </c>
-      <c r="T162">
+      <c r="T162" s="5">
         <v>21.551724</v>
       </c>
     </row>
-    <row r="163" spans="2:20">
-      <c r="B163" t="s">
+    <row r="163" spans="1:20">
+      <c r="A163" s="5"/>
+      <c r="B163" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="C163" t="s">
-        <v>40</v>
-      </c>
-      <c r="D163" t="s">
+      <c r="C163" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D163" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="E163"/>
-      <c r="F163">
-        <v>1</v>
-      </c>
-      <c r="G163" t="s">
+      <c r="E163" s="5"/>
+      <c r="F163" s="5">
+        <v>1</v>
+      </c>
+      <c r="G163" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="H163">
+      <c r="H163" s="5">
         <v>19.827586</v>
       </c>
-      <c r="I163">
+      <c r="I163" s="5">
         <v>32.758620999999998</v>
       </c>
-      <c r="J163" t="s">
-        <v>25</v>
-      </c>
-      <c r="K163" t="s">
-        <v>25</v>
-      </c>
-      <c r="L163" t="s">
+      <c r="J163" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K163" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L163" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="M163" t="s">
-        <v>27</v>
-      </c>
-      <c r="N163" t="s">
-        <v>27</v>
-      </c>
-      <c r="O163" t="s">
-        <v>28</v>
-      </c>
-      <c r="P163">
-        <v>0</v>
-      </c>
-      <c r="Q163">
-        <v>0</v>
-      </c>
-      <c r="R163" t="s">
-        <v>28</v>
-      </c>
-      <c r="S163">
+      <c r="M163" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N163" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O163" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P163" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q163" s="5">
+        <v>0</v>
+      </c>
+      <c r="R163" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="S163" s="5">
         <v>20</v>
       </c>
-      <c r="T163">
+      <c r="T163" s="5">
         <v>29.310345000000002</v>
       </c>
     </row>
-    <row r="164" spans="2:20">
-      <c r="B164" t="s">
+    <row r="164" spans="1:20">
+      <c r="A164" s="5"/>
+      <c r="B164" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C164" t="s">
-        <v>40</v>
-      </c>
-      <c r="D164" t="s">
+      <c r="C164" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D164" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="E164"/>
-      <c r="F164">
-        <v>1</v>
-      </c>
-      <c r="G164" t="s">
+      <c r="E164" s="5"/>
+      <c r="F164" s="5">
+        <v>1</v>
+      </c>
+      <c r="G164" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="H164">
+      <c r="H164" s="5">
         <v>12.931034</v>
       </c>
-      <c r="I164">
+      <c r="I164" s="5">
         <v>19.827586</v>
       </c>
-      <c r="J164" t="s">
-        <v>25</v>
-      </c>
-      <c r="K164" t="s">
-        <v>25</v>
-      </c>
-      <c r="L164" t="s">
+      <c r="J164" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K164" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L164" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="M164" t="s">
-        <v>27</v>
-      </c>
-      <c r="N164" t="s">
-        <v>27</v>
-      </c>
-      <c r="O164" t="s">
-        <v>28</v>
-      </c>
-      <c r="P164">
-        <v>0</v>
-      </c>
-      <c r="Q164">
-        <v>0</v>
-      </c>
-      <c r="R164" t="s">
-        <v>28</v>
-      </c>
-      <c r="S164">
+      <c r="M164" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N164" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O164" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P164" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q164" s="5">
+        <v>0</v>
+      </c>
+      <c r="R164" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="S164" s="5">
         <v>20</v>
       </c>
-      <c r="T164">
+      <c r="T164" s="5">
         <v>18.534483000000002</v>
       </c>
     </row>
-    <row r="165" spans="2:20">
-      <c r="B165" t="s">
+    <row r="165" spans="1:20">
+      <c r="A165" s="5"/>
+      <c r="B165" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="C165" t="s">
+      <c r="C165" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="D165" t="s">
+      <c r="D165" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="E165"/>
-      <c r="F165">
-        <v>1</v>
-      </c>
-      <c r="G165" t="s">
+      <c r="E165" s="5"/>
+      <c r="F165" s="5">
+        <v>1</v>
+      </c>
+      <c r="G165" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="H165">
+      <c r="H165" s="5">
         <v>10.775862</v>
       </c>
-      <c r="I165">
+      <c r="I165" s="5">
         <v>15.948276</v>
       </c>
-      <c r="J165" t="s">
-        <v>25</v>
-      </c>
-      <c r="K165" t="s">
-        <v>25</v>
-      </c>
-      <c r="L165" t="s">
+      <c r="J165" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K165" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L165" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="M165" t="s">
-        <v>27</v>
-      </c>
-      <c r="N165" t="s">
-        <v>27</v>
-      </c>
-      <c r="O165" t="s">
-        <v>28</v>
-      </c>
-      <c r="P165">
-        <v>0</v>
-      </c>
-      <c r="Q165">
-        <v>0</v>
-      </c>
-      <c r="R165" t="s">
-        <v>28</v>
-      </c>
-      <c r="S165">
+      <c r="M165" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N165" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O165" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P165" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q165" s="5">
+        <v>0</v>
+      </c>
+      <c r="R165" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="S165" s="5">
         <v>20</v>
       </c>
-      <c r="T165">
+      <c r="T165" s="5">
         <v>13.793103</v>
       </c>
     </row>
-    <row r="166" spans="2:20">
-      <c r="B166" t="s">
+    <row r="166" spans="1:20">
+      <c r="A166" s="5"/>
+      <c r="B166" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="C166" t="s">
+      <c r="C166" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="D166" t="s">
+      <c r="D166" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="E166"/>
-      <c r="F166">
-        <v>1</v>
-      </c>
-      <c r="G166" t="s">
+      <c r="E166" s="5"/>
+      <c r="F166" s="5">
+        <v>1</v>
+      </c>
+      <c r="G166" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="H166">
+      <c r="H166" s="5">
         <v>10.775862</v>
       </c>
-      <c r="I166">
+      <c r="I166" s="5">
         <v>15.948276</v>
       </c>
-      <c r="J166" t="s">
-        <v>25</v>
-      </c>
-      <c r="K166" t="s">
-        <v>25</v>
-      </c>
-      <c r="L166" t="s">
+      <c r="J166" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K166" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L166" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="M166" t="s">
-        <v>27</v>
-      </c>
-      <c r="N166" t="s">
-        <v>27</v>
-      </c>
-      <c r="O166" t="s">
-        <v>28</v>
-      </c>
-      <c r="P166">
-        <v>0</v>
-      </c>
-      <c r="Q166">
-        <v>0</v>
-      </c>
-      <c r="R166" t="s">
-        <v>28</v>
-      </c>
-      <c r="S166">
+      <c r="M166" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N166" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O166" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P166" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q166" s="5">
+        <v>0</v>
+      </c>
+      <c r="R166" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="S166" s="5">
         <v>20</v>
       </c>
-      <c r="T166">
+      <c r="T166" s="5">
         <v>13.793103</v>
       </c>
     </row>
-    <row r="167" spans="2:20">
-      <c r="B167" t="s">
+    <row r="167" spans="1:20">
+      <c r="A167" s="5"/>
+      <c r="B167" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="C167" t="s">
+      <c r="C167" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D167" t="s">
+      <c r="D167" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="E167"/>
-      <c r="F167">
-        <v>1</v>
-      </c>
-      <c r="G167" t="s">
+      <c r="E167" s="5"/>
+      <c r="F167" s="5">
+        <v>1</v>
+      </c>
+      <c r="G167" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="H167">
+      <c r="H167" s="5">
         <v>12.931034</v>
       </c>
-      <c r="I167">
+      <c r="I167" s="5">
         <v>18.534483000000002</v>
       </c>
-      <c r="J167" t="s">
-        <v>25</v>
-      </c>
-      <c r="K167" t="s">
-        <v>25</v>
-      </c>
-      <c r="L167" t="s">
+      <c r="J167" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K167" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L167" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="M167" t="s">
-        <v>27</v>
-      </c>
-      <c r="N167" t="s">
-        <v>27</v>
-      </c>
-      <c r="O167" t="s">
-        <v>28</v>
-      </c>
-      <c r="P167">
-        <v>0</v>
-      </c>
-      <c r="Q167">
-        <v>0</v>
-      </c>
-      <c r="R167" t="s">
-        <v>28</v>
-      </c>
-      <c r="S167">
+      <c r="M167" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N167" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O167" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P167" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q167" s="5">
+        <v>0</v>
+      </c>
+      <c r="R167" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="S167" s="5">
         <v>20</v>
       </c>
-      <c r="T167">
+      <c r="T167" s="5">
         <v>16.37931</v>
       </c>
     </row>
-    <row r="168" spans="2:20">
-      <c r="B168" t="s">
+    <row r="168" spans="1:20">
+      <c r="A168" s="5"/>
+      <c r="B168" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="C168" t="s">
+      <c r="C168" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D168" t="s">
+      <c r="D168" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="E168"/>
-      <c r="F168">
-        <v>1</v>
-      </c>
-      <c r="G168" t="s">
+      <c r="E168" s="5"/>
+      <c r="F168" s="5">
+        <v>1</v>
+      </c>
+      <c r="G168" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="H168">
+      <c r="H168" s="5">
         <v>12.931034</v>
       </c>
-      <c r="I168">
+      <c r="I168" s="5">
         <v>18.534483000000002</v>
       </c>
-      <c r="J168" t="s">
-        <v>25</v>
-      </c>
-      <c r="K168" t="s">
-        <v>25</v>
-      </c>
-      <c r="L168" t="s">
+      <c r="J168" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K168" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L168" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="M168" t="s">
-        <v>27</v>
-      </c>
-      <c r="N168" t="s">
-        <v>27</v>
-      </c>
-      <c r="O168" t="s">
-        <v>28</v>
-      </c>
-      <c r="P168">
-        <v>0</v>
-      </c>
-      <c r="Q168">
-        <v>0</v>
-      </c>
-      <c r="R168" t="s">
-        <v>28</v>
-      </c>
-      <c r="S168">
+      <c r="M168" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N168" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O168" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P168" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q168" s="5">
+        <v>0</v>
+      </c>
+      <c r="R168" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="S168" s="5">
         <v>20</v>
       </c>
-      <c r="T168">
+      <c r="T168" s="5">
         <v>16.37931</v>
       </c>
     </row>
-    <row r="169" spans="2:20">
-      <c r="B169" t="s">
+    <row r="169" spans="1:20">
+      <c r="A169" s="5"/>
+      <c r="B169" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="C169" t="s">
-        <v>40</v>
-      </c>
-      <c r="D169" t="s">
+      <c r="C169" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D169" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="E169"/>
-      <c r="F169">
-        <v>1</v>
-      </c>
-      <c r="G169" t="s">
+      <c r="E169" s="5"/>
+      <c r="F169" s="5">
+        <v>1</v>
+      </c>
+      <c r="G169" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="H169">
+      <c r="H169" s="5">
         <v>37.068966000000003</v>
       </c>
-      <c r="I169">
+      <c r="I169" s="5">
         <v>51.724138000000004</v>
       </c>
-      <c r="J169" t="s">
-        <v>25</v>
-      </c>
-      <c r="K169" t="s">
-        <v>25</v>
-      </c>
-      <c r="L169" t="s">
+      <c r="J169" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K169" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L169" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="M169" t="s">
-        <v>27</v>
-      </c>
-      <c r="N169" t="s">
-        <v>27</v>
-      </c>
-      <c r="O169" t="s">
-        <v>28</v>
-      </c>
-      <c r="P169">
-        <v>0</v>
-      </c>
-      <c r="Q169">
-        <v>0</v>
-      </c>
-      <c r="R169" t="s">
-        <v>28</v>
-      </c>
-      <c r="S169">
+      <c r="M169" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N169" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O169" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P169" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q169" s="5">
+        <v>0</v>
+      </c>
+      <c r="R169" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="S169" s="5">
         <v>20</v>
       </c>
-      <c r="T169">
+      <c r="T169" s="5">
         <v>50</v>
       </c>
     </row>
-    <row r="170" spans="2:20">
-      <c r="B170" t="s">
+    <row r="170" spans="1:20">
+      <c r="A170" s="5"/>
+      <c r="B170" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="C170" t="s">
+      <c r="C170" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="D170" t="s">
+      <c r="D170" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="E170"/>
-      <c r="F170">
-        <v>1</v>
-      </c>
-      <c r="G170" t="s">
+      <c r="E170" s="5"/>
+      <c r="F170" s="5">
+        <v>1</v>
+      </c>
+      <c r="G170" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="H170">
+      <c r="H170" s="5">
         <v>12.93</v>
       </c>
-      <c r="I170">
+      <c r="I170" s="5">
         <v>18.103448</v>
       </c>
-      <c r="J170" t="s">
-        <v>25</v>
-      </c>
-      <c r="K170" t="s">
-        <v>25</v>
-      </c>
-      <c r="L170" t="s">
+      <c r="J170" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K170" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L170" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="M170" t="s">
-        <v>27</v>
-      </c>
-      <c r="N170" t="s">
-        <v>27</v>
-      </c>
-      <c r="O170" t="s">
-        <v>28</v>
-      </c>
-      <c r="P170">
-        <v>0</v>
-      </c>
-      <c r="Q170">
-        <v>0</v>
-      </c>
-      <c r="R170" t="s">
-        <v>28</v>
-      </c>
-      <c r="S170">
+      <c r="M170" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N170" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O170" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P170" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q170" s="5">
+        <v>0</v>
+      </c>
+      <c r="R170" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="S170" s="5">
         <v>20</v>
       </c>
-      <c r="T170">
+      <c r="T170" s="5">
         <v>16.37931</v>
       </c>
     </row>
-    <row r="171" spans="2:20">
-      <c r="B171" t="s">
+    <row r="171" spans="1:20">
+      <c r="A171" s="5"/>
+      <c r="B171" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="C171" t="s">
+      <c r="C171" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="D171" t="s">
+      <c r="D171" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="E171"/>
-      <c r="F171">
-        <v>1</v>
-      </c>
-      <c r="G171" t="s">
+      <c r="E171" s="5"/>
+      <c r="F171" s="5">
+        <v>1</v>
+      </c>
+      <c r="G171" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="H171">
+      <c r="H171" s="5">
         <v>12.93</v>
       </c>
-      <c r="I171">
+      <c r="I171" s="5">
         <v>18.103448</v>
       </c>
-      <c r="J171" t="s">
-        <v>25</v>
-      </c>
-      <c r="K171" t="s">
-        <v>25</v>
-      </c>
-      <c r="L171" t="s">
+      <c r="J171" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K171" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L171" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="M171" t="s">
-        <v>27</v>
-      </c>
-      <c r="N171" t="s">
-        <v>27</v>
-      </c>
-      <c r="O171" t="s">
-        <v>28</v>
-      </c>
-      <c r="P171">
-        <v>0</v>
-      </c>
-      <c r="Q171">
-        <v>0</v>
-      </c>
-      <c r="R171" t="s">
-        <v>28</v>
-      </c>
-      <c r="S171">
+      <c r="M171" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N171" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O171" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P171" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q171" s="5">
+        <v>0</v>
+      </c>
+      <c r="R171" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="S171" s="5">
         <v>20</v>
       </c>
-      <c r="T171">
+      <c r="T171" s="5">
         <v>16.37931</v>
       </c>
     </row>
-    <row r="172" spans="2:20">
-      <c r="B172" t="s">
+    <row r="172" spans="1:20">
+      <c r="A172" s="5"/>
+      <c r="B172" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="C172" t="s">
+      <c r="C172" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="D172" t="s">
+      <c r="D172" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="E172"/>
-      <c r="F172">
-        <v>1</v>
-      </c>
-      <c r="G172" t="s">
+      <c r="E172" s="5"/>
+      <c r="F172" s="5">
+        <v>1</v>
+      </c>
+      <c r="G172" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="H172">
+      <c r="H172" s="5">
         <v>16.37931</v>
       </c>
-      <c r="I172">
+      <c r="I172" s="5">
         <v>23.706897000000001</v>
       </c>
-      <c r="J172" t="s">
-        <v>25</v>
-      </c>
-      <c r="K172" t="s">
-        <v>25</v>
-      </c>
-      <c r="L172" t="s">
+      <c r="J172" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K172" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L172" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="M172" t="s">
-        <v>27</v>
-      </c>
-      <c r="N172" t="s">
-        <v>27</v>
-      </c>
-      <c r="O172" t="s">
-        <v>28</v>
-      </c>
-      <c r="P172">
-        <v>0</v>
-      </c>
-      <c r="Q172">
-        <v>0</v>
-      </c>
-      <c r="R172" t="s">
-        <v>28</v>
-      </c>
-      <c r="S172">
+      <c r="M172" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N172" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O172" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P172" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q172" s="5">
+        <v>0</v>
+      </c>
+      <c r="R172" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="S172" s="5">
         <v>20</v>
       </c>
-      <c r="T172">
+      <c r="T172" s="5">
         <v>18.965516999999998</v>
       </c>
     </row>
-    <row r="173" spans="2:20">
-      <c r="B173" t="s">
+    <row r="173" spans="1:20">
+      <c r="A173" s="5"/>
+      <c r="B173" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="C173" t="s">
+      <c r="C173" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="D173" t="s">
+      <c r="D173" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="E173"/>
-      <c r="F173">
-        <v>1</v>
-      </c>
-      <c r="G173" t="s">
+      <c r="E173" s="5"/>
+      <c r="F173" s="5">
+        <v>1</v>
+      </c>
+      <c r="G173" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="H173">
+      <c r="H173" s="5">
         <v>17.239999999999998</v>
       </c>
-      <c r="I173">
+      <c r="I173" s="5">
         <v>23.706897000000001</v>
       </c>
-      <c r="J173" t="s">
-        <v>25</v>
-      </c>
-      <c r="K173" t="s">
-        <v>25</v>
-      </c>
-      <c r="L173" t="s">
+      <c r="J173" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K173" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L173" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="M173" t="s">
-        <v>27</v>
-      </c>
-      <c r="N173" t="s">
-        <v>27</v>
-      </c>
-      <c r="O173" t="s">
-        <v>28</v>
-      </c>
-      <c r="P173">
-        <v>0</v>
-      </c>
-      <c r="Q173">
-        <v>0</v>
-      </c>
-      <c r="R173" t="s">
-        <v>28</v>
-      </c>
-      <c r="S173">
+      <c r="M173" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N173" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O173" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P173" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q173" s="5">
+        <v>0</v>
+      </c>
+      <c r="R173" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="S173" s="5">
         <v>20</v>
       </c>
-      <c r="T173">
+      <c r="T173" s="5">
         <v>18.965516999999998</v>
       </c>
     </row>
-    <row r="174" spans="2:20">
-      <c r="B174" t="s">
+    <row r="174" spans="1:20">
+      <c r="A174" s="5"/>
+      <c r="B174" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="C174" t="s">
-        <v>40</v>
-      </c>
-      <c r="D174" t="s">
+      <c r="C174" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D174" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="E174"/>
-      <c r="F174">
-        <v>1</v>
-      </c>
-      <c r="G174" t="s">
+      <c r="E174" s="5"/>
+      <c r="F174" s="5">
+        <v>1</v>
+      </c>
+      <c r="G174" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="H174">
+      <c r="H174" s="5">
         <v>3.88</v>
       </c>
-      <c r="I174">
+      <c r="I174" s="5">
         <v>8.4482759999999999</v>
       </c>
-      <c r="J174" t="s">
-        <v>25</v>
-      </c>
-      <c r="K174" t="s">
-        <v>25</v>
-      </c>
-      <c r="L174" t="s">
+      <c r="J174" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K174" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L174" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="M174" t="s">
-        <v>27</v>
-      </c>
-      <c r="N174" t="s">
-        <v>27</v>
-      </c>
-      <c r="O174" t="s">
-        <v>28</v>
-      </c>
-      <c r="P174">
-        <v>0</v>
-      </c>
-      <c r="Q174">
-        <v>0</v>
-      </c>
-      <c r="R174" t="s">
-        <v>28</v>
-      </c>
-      <c r="S174">
+      <c r="M174" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N174" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O174" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P174" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q174" s="5">
+        <v>0</v>
+      </c>
+      <c r="R174" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="S174" s="5">
         <v>20</v>
       </c>
-      <c r="T174">
+      <c r="T174" s="5">
         <v>6.0344829999999998</v>
       </c>
     </row>
-    <row r="175" spans="2:20">
-      <c r="B175" t="s">
+    <row r="175" spans="1:20">
+      <c r="A175" s="5"/>
+      <c r="B175" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="C175" t="s">
+      <c r="C175" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="D175" t="s">
+      <c r="D175" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="E175"/>
-      <c r="F175">
-        <v>1</v>
-      </c>
-      <c r="G175" t="s">
+      <c r="E175" s="5"/>
+      <c r="F175" s="5">
+        <v>1</v>
+      </c>
+      <c r="G175" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="H175">
+      <c r="H175" s="5">
         <v>3.0172409999999998</v>
       </c>
-      <c r="I175">
+      <c r="I175" s="5">
         <v>6.4655170000000002</v>
       </c>
-      <c r="J175" t="s">
-        <v>25</v>
-      </c>
-      <c r="K175" t="s">
-        <v>25</v>
-      </c>
-      <c r="L175" t="s">
+      <c r="J175" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K175" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L175" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="M175" t="s">
-        <v>27</v>
-      </c>
-      <c r="N175" t="s">
-        <v>27</v>
-      </c>
-      <c r="O175" t="s">
-        <v>28</v>
-      </c>
-      <c r="P175">
-        <v>0</v>
-      </c>
-      <c r="Q175">
-        <v>0</v>
-      </c>
-      <c r="R175" t="s">
-        <v>28</v>
-      </c>
-      <c r="S175">
+      <c r="M175" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N175" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O175" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P175" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q175" s="5">
+        <v>0</v>
+      </c>
+      <c r="R175" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="S175" s="5">
         <v>20</v>
       </c>
-      <c r="T175">
+      <c r="T175" s="5">
         <v>5.1724139999999998</v>
       </c>
     </row>
-    <row r="176" spans="2:20">
-      <c r="B176" t="s">
+    <row r="176" spans="1:20">
+      <c r="A176" s="5"/>
+      <c r="B176" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="C176" t="s">
+      <c r="C176" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="D176" t="s">
+      <c r="D176" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="E176"/>
-      <c r="F176">
-        <v>1</v>
-      </c>
-      <c r="G176" t="s">
+      <c r="E176" s="5"/>
+      <c r="F176" s="5">
+        <v>1</v>
+      </c>
+      <c r="G176" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="H176">
+      <c r="H176" s="5">
         <v>3.0172409999999998</v>
       </c>
-      <c r="I176">
+      <c r="I176" s="5">
         <v>6.4655170000000002</v>
       </c>
-      <c r="J176" t="s">
-        <v>25</v>
-      </c>
-      <c r="K176" t="s">
-        <v>25</v>
-      </c>
-      <c r="L176" t="s">
+      <c r="J176" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K176" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L176" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="M176" t="s">
-        <v>27</v>
-      </c>
-      <c r="N176" t="s">
-        <v>27</v>
-      </c>
-      <c r="O176" t="s">
-        <v>28</v>
-      </c>
-      <c r="P176">
-        <v>0</v>
-      </c>
-      <c r="Q176">
-        <v>0</v>
-      </c>
-      <c r="R176" t="s">
-        <v>28</v>
-      </c>
-      <c r="S176">
+      <c r="M176" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N176" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O176" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P176" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q176" s="5">
+        <v>0</v>
+      </c>
+      <c r="R176" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="S176" s="5">
         <v>20</v>
       </c>
-      <c r="T176">
+      <c r="T176" s="5">
         <v>5.1724139999999998</v>
       </c>
     </row>
-    <row r="177" spans="2:20">
-      <c r="B177" t="s">
+    <row r="177" spans="1:20">
+      <c r="A177" s="5"/>
+      <c r="B177" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="C177" t="s">
+      <c r="C177" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="D177" t="s">
+      <c r="D177" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="E177"/>
-      <c r="F177">
-        <v>1</v>
-      </c>
-      <c r="G177" t="s">
+      <c r="E177" s="5"/>
+      <c r="F177" s="5">
+        <v>1</v>
+      </c>
+      <c r="G177" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="H177">
+      <c r="H177" s="5">
         <v>3.0172409999999998</v>
       </c>
-      <c r="I177">
+      <c r="I177" s="5">
         <v>6.4655170000000002</v>
       </c>
-      <c r="J177" t="s">
-        <v>25</v>
-      </c>
-      <c r="K177" t="s">
-        <v>25</v>
-      </c>
-      <c r="L177" t="s">
+      <c r="J177" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K177" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L177" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="M177" t="s">
-        <v>27</v>
-      </c>
-      <c r="N177" t="s">
-        <v>27</v>
-      </c>
-      <c r="O177" t="s">
-        <v>28</v>
-      </c>
-      <c r="P177">
-        <v>0</v>
-      </c>
-      <c r="Q177">
-        <v>0</v>
-      </c>
-      <c r="R177" t="s">
-        <v>28</v>
-      </c>
-      <c r="S177">
+      <c r="M177" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N177" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O177" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P177" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q177" s="5">
+        <v>0</v>
+      </c>
+      <c r="R177" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="S177" s="5">
         <v>20</v>
       </c>
-      <c r="T177">
+      <c r="T177" s="5">
         <v>5.1724139999999998</v>
       </c>
     </row>
-    <row r="178" spans="2:20">
-      <c r="B178" t="s">
+    <row r="178" spans="1:20">
+      <c r="A178" s="5"/>
+      <c r="B178" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="C178" t="s">
+      <c r="C178" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="D178" t="s">
+      <c r="D178" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="E178"/>
-      <c r="F178">
-        <v>1</v>
-      </c>
-      <c r="G178" t="s">
+      <c r="E178" s="5"/>
+      <c r="F178" s="5">
+        <v>1</v>
+      </c>
+      <c r="G178" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="H178">
+      <c r="H178" s="5">
         <v>5.6034480000000002</v>
       </c>
-      <c r="I178">
+      <c r="I178" s="5">
         <v>9.9137930000000001</v>
       </c>
-      <c r="J178" t="s">
-        <v>25</v>
-      </c>
-      <c r="K178" t="s">
-        <v>25</v>
-      </c>
-      <c r="L178" t="s">
+      <c r="J178" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K178" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L178" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="M178" t="s">
-        <v>27</v>
-      </c>
-      <c r="N178" t="s">
-        <v>27</v>
-      </c>
-      <c r="O178" t="s">
-        <v>28</v>
-      </c>
-      <c r="P178">
-        <v>0</v>
-      </c>
-      <c r="Q178">
-        <v>0</v>
-      </c>
-      <c r="R178" t="s">
-        <v>28</v>
-      </c>
-      <c r="S178">
+      <c r="M178" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N178" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O178" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P178" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q178" s="5">
+        <v>0</v>
+      </c>
+      <c r="R178" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="S178" s="5">
         <v>20</v>
       </c>
-      <c r="T178">
+      <c r="T178" s="5">
         <v>6.8965519999999998</v>
       </c>
     </row>
-    <row r="179" spans="2:20">
-      <c r="B179" t="s">
+    <row r="179" spans="1:20">
+      <c r="A179" s="5"/>
+      <c r="B179" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="C179" t="s">
+      <c r="C179" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="D179" t="s">
+      <c r="D179" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="E179"/>
-      <c r="F179">
-        <v>1</v>
-      </c>
-      <c r="G179" t="s">
+      <c r="E179" s="5"/>
+      <c r="F179" s="5">
+        <v>1</v>
+      </c>
+      <c r="G179" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="H179">
+      <c r="H179" s="5">
         <v>6.4655170000000002</v>
       </c>
-      <c r="I179">
+      <c r="I179" s="5">
         <v>11.637931</v>
       </c>
-      <c r="J179" t="s">
-        <v>25</v>
-      </c>
-      <c r="K179" t="s">
-        <v>25</v>
-      </c>
-      <c r="L179" t="s">
+      <c r="J179" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K179" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L179" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="M179" t="s">
-        <v>27</v>
-      </c>
-      <c r="N179" t="s">
-        <v>27</v>
-      </c>
-      <c r="O179" t="s">
-        <v>28</v>
-      </c>
-      <c r="P179">
-        <v>0</v>
-      </c>
-      <c r="Q179">
-        <v>0</v>
-      </c>
-      <c r="R179" t="s">
-        <v>28</v>
-      </c>
-      <c r="S179">
+      <c r="M179" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N179" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O179" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P179" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q179" s="5">
+        <v>0</v>
+      </c>
+      <c r="R179" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="S179" s="5">
         <v>20</v>
       </c>
-      <c r="T179">
+      <c r="T179" s="5">
         <v>8.1896550000000001</v>
       </c>
     </row>
-    <row r="180" spans="2:20">
-      <c r="B180" t="s">
+    <row r="180" spans="1:20">
+      <c r="A180" s="5"/>
+      <c r="B180" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="C180" t="s">
-        <v>40</v>
-      </c>
-      <c r="D180" t="s">
+      <c r="C180" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D180" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="E180"/>
-      <c r="F180">
-        <v>1</v>
-      </c>
-      <c r="G180" t="s">
+      <c r="E180" s="5"/>
+      <c r="F180" s="5">
+        <v>1</v>
+      </c>
+      <c r="G180" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="H180">
+      <c r="H180" s="5">
         <v>8.6206899999999997</v>
       </c>
-      <c r="I180">
+      <c r="I180" s="5">
         <v>13.793103</v>
       </c>
-      <c r="J180" t="s">
-        <v>25</v>
-      </c>
-      <c r="K180" t="s">
-        <v>25</v>
-      </c>
-      <c r="L180" t="s">
+      <c r="J180" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K180" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L180" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="M180" t="s">
-        <v>27</v>
-      </c>
-      <c r="N180" t="s">
-        <v>27</v>
-      </c>
-      <c r="O180" t="s">
-        <v>28</v>
-      </c>
-      <c r="P180">
-        <v>0</v>
-      </c>
-      <c r="Q180">
-        <v>0</v>
-      </c>
-      <c r="R180" t="s">
-        <v>28</v>
-      </c>
-      <c r="S180">
+      <c r="M180" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N180" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O180" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P180" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q180" s="5">
+        <v>0</v>
+      </c>
+      <c r="R180" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="S180" s="5">
         <v>20</v>
       </c>
-      <c r="T180">
+      <c r="T180" s="5">
         <v>10.344828</v>
       </c>
     </row>
-    <row r="181" spans="2:20">
-      <c r="B181" t="s">
+    <row r="181" spans="1:20">
+      <c r="A181" s="5"/>
+      <c r="B181" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="C181" t="s">
-        <v>40</v>
-      </c>
-      <c r="D181" t="s">
+      <c r="C181" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D181" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="E181"/>
-      <c r="F181">
-        <v>1</v>
-      </c>
-      <c r="G181" t="s">
+      <c r="E181" s="5"/>
+      <c r="F181" s="5">
+        <v>1</v>
+      </c>
+      <c r="G181" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="H181">
+      <c r="H181" s="5">
         <v>7.33</v>
       </c>
-      <c r="I181">
+      <c r="I181" s="5">
         <v>18.103448</v>
       </c>
-      <c r="J181" t="s">
-        <v>25</v>
-      </c>
-      <c r="K181" t="s">
-        <v>25</v>
-      </c>
-      <c r="L181" t="s">
+      <c r="J181" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K181" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L181" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="M181" t="s">
-        <v>27</v>
-      </c>
-      <c r="N181" t="s">
-        <v>27</v>
-      </c>
-      <c r="O181" t="s">
-        <v>28</v>
-      </c>
-      <c r="P181">
-        <v>0</v>
-      </c>
-      <c r="Q181">
-        <v>0</v>
-      </c>
-      <c r="R181" t="s">
-        <v>28</v>
-      </c>
-      <c r="S181">
+      <c r="M181" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N181" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O181" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P181" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q181" s="5">
+        <v>0</v>
+      </c>
+      <c r="R181" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="S181" s="5">
         <v>20</v>
       </c>
-      <c r="T181">
+      <c r="T181" s="5">
         <v>12.931034</v>
       </c>
     </row>
-    <row r="182" spans="2:20">
-      <c r="B182" t="s">
+    <row r="182" spans="1:20">
+      <c r="A182" s="5"/>
+      <c r="B182" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="C182" t="s">
+      <c r="C182" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="D182" t="s">
+      <c r="D182" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="E182"/>
-      <c r="F182">
-        <v>1</v>
-      </c>
-      <c r="G182" t="s">
+      <c r="E182" s="5"/>
+      <c r="F182" s="5">
+        <v>1</v>
+      </c>
+      <c r="G182" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="H182">
+      <c r="H182" s="5">
         <v>6.0344829999999998</v>
       </c>
-      <c r="I182">
+      <c r="I182" s="5">
         <v>10.344828</v>
       </c>
-      <c r="J182" t="s">
-        <v>25</v>
-      </c>
-      <c r="K182" t="s">
-        <v>25</v>
-      </c>
-      <c r="L182" t="s">
+      <c r="J182" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K182" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L182" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="M182" t="s">
-        <v>27</v>
-      </c>
-      <c r="N182" t="s">
-        <v>27</v>
-      </c>
-      <c r="O182" t="s">
-        <v>28</v>
-      </c>
-      <c r="P182">
-        <v>0</v>
-      </c>
-      <c r="Q182">
-        <v>0</v>
-      </c>
-      <c r="R182" t="s">
-        <v>28</v>
-      </c>
-      <c r="S182">
+      <c r="M182" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N182" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O182" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P182" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q182" s="5">
+        <v>0</v>
+      </c>
+      <c r="R182" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="S182" s="5">
         <v>20</v>
       </c>
-      <c r="T182">
+      <c r="T182" s="5">
         <v>8.1896550000000001</v>
       </c>
     </row>
-    <row r="183" spans="2:20">
-      <c r="B183" t="s">
+    <row r="183" spans="1:20">
+      <c r="A183" s="5"/>
+      <c r="B183" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="C183" t="s">
+      <c r="C183" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="D183" t="s">
+      <c r="D183" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="E183"/>
-      <c r="F183">
-        <v>1</v>
-      </c>
-      <c r="G183" t="s">
+      <c r="E183" s="5"/>
+      <c r="F183" s="5">
+        <v>1</v>
+      </c>
+      <c r="G183" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="H183">
+      <c r="H183" s="5">
         <v>6.0344829999999998</v>
       </c>
-      <c r="I183">
+      <c r="I183" s="5">
         <v>10.344828</v>
       </c>
-      <c r="J183" t="s">
-        <v>25</v>
-      </c>
-      <c r="K183" t="s">
-        <v>25</v>
-      </c>
-      <c r="L183" t="s">
+      <c r="J183" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K183" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L183" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="M183" t="s">
-        <v>27</v>
-      </c>
-      <c r="N183" t="s">
-        <v>27</v>
-      </c>
-      <c r="O183" t="s">
-        <v>28</v>
-      </c>
-      <c r="P183">
-        <v>0</v>
-      </c>
-      <c r="Q183">
-        <v>0</v>
-      </c>
-      <c r="R183" t="s">
-        <v>28</v>
-      </c>
-      <c r="S183">
+      <c r="M183" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N183" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O183" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P183" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q183" s="5">
+        <v>0</v>
+      </c>
+      <c r="R183" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="S183" s="5">
         <v>20</v>
       </c>
-      <c r="T183">
+      <c r="T183" s="5">
         <v>8.1896550000000001</v>
       </c>
     </row>
-    <row r="184" spans="2:20">
-      <c r="B184" t="s">
+    <row r="184" spans="1:20">
+      <c r="A184" s="5"/>
+      <c r="B184" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="C184" t="s">
+      <c r="C184" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="D184" t="s">
+      <c r="D184" s="5" t="s">
         <v>316</v>
       </c>
-      <c r="E184"/>
-      <c r="F184">
-        <v>1</v>
-      </c>
-      <c r="G184" t="s">
+      <c r="E184" s="5"/>
+      <c r="F184" s="5">
+        <v>1</v>
+      </c>
+      <c r="G184" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="H184">
+      <c r="H184" s="5">
         <v>6.0344829999999998</v>
       </c>
-      <c r="I184">
+      <c r="I184" s="5">
         <v>10.344828</v>
       </c>
-      <c r="J184" t="s">
-        <v>25</v>
-      </c>
-      <c r="K184" t="s">
-        <v>25</v>
-      </c>
-      <c r="L184" t="s">
+      <c r="J184" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K184" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L184" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="M184" t="s">
-        <v>27</v>
-      </c>
-      <c r="N184" t="s">
-        <v>27</v>
-      </c>
-      <c r="O184" t="s">
-        <v>28</v>
-      </c>
-      <c r="P184">
-        <v>0</v>
-      </c>
-      <c r="Q184">
-        <v>0</v>
-      </c>
-      <c r="R184" t="s">
-        <v>28</v>
-      </c>
-      <c r="S184">
+      <c r="M184" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N184" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O184" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P184" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q184" s="5">
+        <v>0</v>
+      </c>
+      <c r="R184" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="S184" s="5">
         <v>20</v>
       </c>
-      <c r="T184">
+      <c r="T184" s="5">
         <v>8.1896550000000001</v>
       </c>
     </row>
-    <row r="185" spans="2:20">
-      <c r="B185" t="s">
+    <row r="185" spans="1:20">
+      <c r="A185" s="5"/>
+      <c r="B185" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="C185" t="s">
+      <c r="C185" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="D185" t="s">
+      <c r="D185" s="5" t="s">
         <v>318</v>
       </c>
-      <c r="E185"/>
-      <c r="F185">
-        <v>1</v>
-      </c>
-      <c r="G185" t="s">
+      <c r="E185" s="5"/>
+      <c r="F185" s="5">
+        <v>1</v>
+      </c>
+      <c r="G185" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="I185">
+      <c r="H185" s="5"/>
+      <c r="I185" s="5">
         <v>47.413792999999998</v>
       </c>
-      <c r="J185" t="s">
-        <v>25</v>
-      </c>
-      <c r="K185" t="s">
-        <v>25</v>
-      </c>
-      <c r="L185" t="s">
+      <c r="J185" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K185" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L185" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="M185" t="s">
-        <v>27</v>
-      </c>
-      <c r="N185" t="s">
-        <v>27</v>
-      </c>
-      <c r="O185" t="s">
-        <v>28</v>
-      </c>
-      <c r="P185">
-        <v>0</v>
-      </c>
-      <c r="Q185">
-        <v>0</v>
-      </c>
-      <c r="R185" t="s">
-        <v>28</v>
-      </c>
-      <c r="S185">
+      <c r="M185" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N185" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O185" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P185" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q185" s="5">
+        <v>0</v>
+      </c>
+      <c r="R185" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="S185" s="5">
         <v>20</v>
       </c>
-      <c r="T185">
+      <c r="T185" s="5">
         <v>44.827585999999997</v>
       </c>
     </row>
-    <row r="186" spans="2:20">
+    <row r="186" spans="1:20">
       <c r="B186" t="s">
         <v>319</v>
       </c>
@@ -12232,7 +12269,7 @@
         <v>13.793103</v>
       </c>
     </row>
-    <row r="187" spans="2:20">
+    <row r="187" spans="1:20">
       <c r="B187" t="s">
         <v>321</v>
       </c>
@@ -12286,7 +12323,7 @@
         <v>30.172414</v>
       </c>
     </row>
-    <row r="188" spans="2:20">
+    <row r="188" spans="1:20">
       <c r="B188" t="s">
         <v>323</v>
       </c>
@@ -12340,7 +12377,7 @@
         <v>38.793103000000002</v>
       </c>
     </row>
-    <row r="189" spans="2:20">
+    <row r="189" spans="1:20">
       <c r="B189" t="s">
         <v>325</v>
       </c>
@@ -12394,7 +12431,7 @@
         <v>22.413792999999998</v>
       </c>
     </row>
-    <row r="190" spans="2:20">
+    <row r="190" spans="1:20">
       <c r="B190" t="s">
         <v>327</v>
       </c>
@@ -12448,7 +12485,7 @@
         <v>22.413792999999998</v>
       </c>
     </row>
-    <row r="191" spans="2:20">
+    <row r="191" spans="1:20">
       <c r="B191" t="s">
         <v>328</v>
       </c>
@@ -12502,7 +12539,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="192" spans="2:20">
+    <row r="192" spans="1:20">
       <c r="B192" t="s">
         <v>330</v>
       </c>
